--- a/tests/sample_artifacts/invalid/excel/invalid_customers_multiple_datasets.xlsx
+++ b/tests/sample_artifacts/invalid/excel/invalid_customers_multiple_datasets.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DATA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Customers_AU" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Customers_US" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,116 +442,507 @@
           <t>CreditLimit</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CUST90001</t>
+          <t>CUST01100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bad Data 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+          <t>Customer 1100</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>45299</v>
       </c>
       <c r="D2" t="n">
-        <v>2500</v>
+        <v>1550</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CUST90002</t>
+          <t>CUST01101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bad Data 2</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>01/02/2025</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2025-03-05</t>
+          <t>Customer 1101</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1585.75</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CRM</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST01102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer 1102</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1621.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CustomerId</t>
+          <t>CUST01103</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CustomerName</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SignupDate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CreditLimit</t>
+          <t>Customer 1103</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1657.25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CRM</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CUST99991</t>
+          <t>CustomerId</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Second Dataset 1</t>
+          <t>CustomerName</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31/13/2025</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1500</v>
+          <t>SignupDate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CreditLimit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CUST99992</t>
+          <t>CUST01100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Second Dataset 2</t>
+          <t>Customer 1100</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>31/13/2025</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CUST01101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Customer 1101</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>ABC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>CustomerId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>CustomerName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>SignupDate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CreditLimit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IsActive</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RegionCode</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SourceSystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CUST02100</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Customer 2100</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>45299</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CUST02101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer 2101</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>45300</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1585.75</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CUST02102</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Customer 2102</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1621.5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CUST02103</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Customer 2103</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>45302</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1657.25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CUST02104</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer 2104</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>45303</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1693</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CUST02105</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Customer 2105</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>45304</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1728.75</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CRM</t>
         </is>
       </c>
     </row>
